--- a/data/trans_orig/P2C_R1-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P2C_R1-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son remunerados en 2007</t>
+          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son remunerados en 2007 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7239</t>
+          <t>7165</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8140</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1199</t>
+          <t>1127</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11554</t>
+          <t>10796</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>415864</t>
+          <t>415938</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>483894</t>
+          <t>483988</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>903583</t>
+          <t>904341</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>913938</t>
+          <t>914010</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>99,88%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1064</t>
+          <t>1058</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14072</t>
+          <t>13807</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2762</t>
+          <t>3106</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15465</t>
+          <t>15774</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5793</t>
+          <t>4765</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21776</t>
+          <t>21333</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>572437</t>
+          <t>572702</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>585445</t>
+          <t>585451</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>634697</t>
+          <t>634388</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>647400</t>
+          <t>647056</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1214895</t>
+          <t>1215338</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1230878</t>
+          <t>1231906</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,61%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>964</t>
+          <t>976</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8674</t>
+          <t>8795</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>976</t>
+          <t>978</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8488</t>
+          <t>8739</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>401370</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>403381</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>467431</t>
+          <t>467310</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>475141</t>
+          <t>475129</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>870998</t>
+          <t>870747</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>878510</t>
+          <t>878508</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1680</t>
+          <t>1696</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9491</t>
+          <t>9545</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1653</t>
+          <t>1229</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12300</t>
+          <t>12125</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4432</t>
+          <t>4216</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16990</t>
+          <t>17337</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>487741</t>
+          <t>487687</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>495552</t>
+          <t>495536</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>670762</t>
+          <t>670937</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>681409</t>
+          <t>681833</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1163304</t>
+          <t>1162957</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1175862</t>
+          <t>1176078</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,64%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4736</t>
+          <t>5479</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20677</t>
+          <t>20075</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10664</t>
+          <t>10194</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>29730</t>
+          <t>28173</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>19490</t>
+          <t>18664</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>44763</t>
+          <t>41428</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,98%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1889549</t>
+          <t>1890151</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1905490</t>
+          <t>1904747</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2271632</t>
+          <t>2273189</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2290698</t>
+          <t>2291168</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4166825</t>
+          <t>4170160</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4192098</t>
+          <t>4192924</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,56%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son remunerados en 2012</t>
+          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son remunerados en 2012 (tasa de respuesta: 99,27%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2685,7 +2685,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6653</t>
+          <t>7994</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2125</t>
+          <t>2051</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12042</t>
+          <t>12271</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3278</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16488</t>
+          <t>16771</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>465859</t>
+          <t>464518</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>502565</t>
+          <t>502336</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>512482</t>
+          <t>512556</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>970631</t>
+          <t>970348</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>983841</t>
+          <t>983590</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,64%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>962</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8702</t>
+          <t>8670</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>1102</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11997</t>
+          <t>13402</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3649</t>
+          <t>3397</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17336</t>
+          <t>17443</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>652837</t>
+          <t>652869</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>660585</t>
+          <t>660577</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>734853</t>
+          <t>733448</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>745749</t>
+          <t>745748</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1391053</t>
+          <t>1390946</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1404740</t>
+          <t>1404992</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,76%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1811</t>
+          <t>988</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13024</t>
+          <t>12748</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,47 +3381,47 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2,79%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>6025</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>2120</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>14214</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>1,13%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
           <t>0,4%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,85%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>6025</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>2086</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>13142</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,13%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4998</t>
+          <t>4948</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20561</t>
+          <t>19981</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>444205</t>
+          <t>444481</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>455418</t>
+          <t>456241</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,49 +3494,49 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
+          <t>99,78%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>482</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>525696</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>517507</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>529601</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>98,87%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>97,33%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
           <t>99,6%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>482</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>525696</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>518579</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>529635</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>98,87%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>97,53%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>99,61%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>897</t>
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>968389</t>
+          <t>968969</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>983952</t>
+          <t>984002</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,5%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1923</t>
+          <t>1915</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14581</t>
+          <t>13697</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6819</t>
+          <t>6855</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22268</t>
+          <t>22420</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10904</t>
+          <t>10739</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>29516</t>
+          <t>29038</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>531465</t>
+          <t>532349</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>544123</t>
+          <t>544131</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>701384</t>
+          <t>701232</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>716833</t>
+          <t>716797</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1240182</t>
+          <t>1240660</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1258794</t>
+          <t>1258959</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,15%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9457</t>
+          <t>9727</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26765</t>
+          <t>28419</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18997</t>
+          <t>18056</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>41757</t>
+          <t>41584</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>32174</t>
+          <t>31692</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>61541</t>
+          <t>61375</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2110561</t>
+          <t>2108907</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2127869</t>
+          <t>2127599</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2475073</t>
+          <t>2475246</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2497833</t>
+          <t>2498774</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4592615</t>
+          <t>4592781</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4621982</t>
+          <t>4622464</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4255,7 +4255,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,32%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son remunerados en 2016</t>
+          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son remunerados en 2016 (tasa de respuesta: 94,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3001</t>
+          <t>3014</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13361</t>
+          <t>13949</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4667,7 +4667,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6559</t>
+          <t>6588</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3883</t>
+          <t>4212</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15491</t>
+          <t>16416</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>384600</t>
+          <t>384012</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>394960</t>
+          <t>394947</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,7 +4775,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>439909</t>
+          <t>439880</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>828938</t>
+          <t>828013</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>840546</t>
+          <t>840217</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,5%</t>
         </is>
       </c>
     </row>
@@ -4975,7 +4975,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10407</t>
+          <t>8514</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2075</t>
+          <t>2065</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12900</t>
+          <t>11756</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5025,7 +5025,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3247</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17007</t>
+          <t>16027</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -5083,7 +5083,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>571926</t>
+          <t>573819</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>704114</t>
+          <t>705258</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>714939</t>
+          <t>714949</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1282340</t>
+          <t>1283320</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1296100</t>
+          <t>1296120</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,7 +5168,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -5318,7 +5318,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7295</t>
+          <t>7853</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5333,7 +5333,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2307</t>
+          <t>2312</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13245</t>
+          <t>13882</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4252</t>
+          <t>4240</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17974</t>
+          <t>16140</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>408862</t>
+          <t>408304</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>500069</t>
+          <t>499432</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>511007</t>
+          <t>511002</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>911497</t>
+          <t>913331</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>925219</t>
+          <t>925231</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2277</t>
+          <t>2604</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11900</t>
+          <t>12455</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3663</t>
+          <t>4009</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16485</t>
+          <t>17422</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8343</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>24140</t>
+          <t>25271</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,18%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>488577</t>
+          <t>488022</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>498200</t>
+          <t>497873</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>641739</t>
+          <t>640802</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>654561</t>
+          <t>654215</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1134561</t>
+          <t>1133430</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1150358</t>
+          <t>1150649</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,31%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10603</t>
+          <t>10835</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27109</t>
+          <t>27175</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,7 +6014,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14413</t>
+          <t>14921</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>35890</t>
+          <t>33490</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>29413</t>
+          <t>28035</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>54728</t>
+          <t>54523</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,7 +6084,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1869819</t>
+          <t>1869753</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1886325</t>
+          <t>1886093</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6132,7 +6132,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2299130</t>
+          <t>2301530</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2320607</t>
+          <t>2320099</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4177220</t>
+          <t>4177425</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4202535</t>
+          <t>4203913</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,34%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son remunerados en 2023</t>
+          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son remunerados en 2023 (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19631</t>
+          <t>19160</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35309</t>
+          <t>33825</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>33,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>29843</t>
+          <t>30162</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>44773</t>
+          <t>43738</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>32,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>51991</t>
+          <t>52038</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>73151</t>
+          <t>74228</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>31,43%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>64920</t>
+          <t>66404</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>80598</t>
+          <t>81069</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>64,77%</t>
+          <t>66,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,41%</t>
+          <t>80,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>91182</t>
+          <t>92217</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>106112</t>
+          <t>105793</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>67,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78,05%</t>
+          <t>77,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>163033</t>
+          <t>161956</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>184193</t>
+          <t>184146</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>69,03%</t>
+          <t>68,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>77,99%</t>
+          <t>77,97%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15302</t>
+          <t>15490</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33792</t>
+          <t>33945</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29590</t>
+          <t>29900</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>46871</t>
+          <t>46988</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>49359</t>
+          <t>48651</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>74122</t>
+          <t>73907</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,17%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>127794</t>
+          <t>127641</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>146284</t>
+          <t>146096</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,09%</t>
+          <t>78,99%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,41%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>198288</t>
+          <t>198171</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>215569</t>
+          <t>215259</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,88%</t>
+          <t>80,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>332623</t>
+          <t>332838</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>357386</t>
+          <t>358094</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,78%</t>
+          <t>81,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>88,04%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8779</t>
+          <t>9172</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24111</t>
+          <t>24478</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2851</t>
+          <t>3960</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>40771</t>
+          <t>43165</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8308</t>
+          <t>9461</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>62122</t>
+          <t>63213</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,55%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>77197</t>
+          <t>76830</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>92529</t>
+          <t>92136</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,2%</t>
+          <t>75,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>292359</t>
+          <t>289965</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>330279</t>
+          <t>329170</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>87,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>372316</t>
+          <t>371225</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>426130</t>
+          <t>424977</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>97,82%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10727</t>
+          <t>10563</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23808</t>
+          <t>24979</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24530</t>
+          <t>24682</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>41705</t>
+          <t>40871</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>38637</t>
+          <t>38359</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>59887</t>
+          <t>60599</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,63%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>102321</t>
+          <t>101150</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>115402</t>
+          <t>115566</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,12%</t>
+          <t>80,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>140885</t>
+          <t>141719</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>158060</t>
+          <t>157908</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,16%</t>
+          <t>77,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,57%</t>
+          <t>86,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>248833</t>
+          <t>248121</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>270083</t>
+          <t>270361</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,6%</t>
+          <t>80,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,48%</t>
+          <t>87,57%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>66947</t>
+          <t>66767</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>97983</t>
+          <t>99445</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>57911</t>
+          <t>64709</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>162248</t>
+          <t>162854</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>120183</t>
+          <t>118878</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>245408</t>
+          <t>245815</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,73%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>391270</t>
+          <t>389808</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>422306</t>
+          <t>422486</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,97%</t>
+          <t>79,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>86,35%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>734586</t>
+          <t>733980</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>838923</t>
+          <t>832125</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,91%</t>
+          <t>81,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1140679</t>
+          <t>1140272</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1265904</t>
+          <t>1267209</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,29%</t>
+          <t>82,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,42%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P2C_R1-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P2C_R1-Habitat-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7165</t>
+          <t>7229</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1127</t>
+          <t>1124</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10796</t>
+          <t>9842</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>415938</t>
+          <t>415874</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>483988</t>
+          <t>483824</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>904341</t>
+          <t>905295</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>914010</t>
+          <t>914013</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13807</t>
+          <t>13934</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3106</t>
+          <t>3382</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15774</t>
+          <t>16382</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4765</t>
+          <t>6010</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21333</t>
+          <t>22154</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>572702</t>
+          <t>572575</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>634388</t>
+          <t>633780</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>647056</t>
+          <t>646780</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1215338</t>
+          <t>1214517</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1231906</t>
+          <t>1230661</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,51%</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>976</t>
+          <t>973</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8795</t>
+          <t>8730</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>978</t>
+          <t>975</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8739</t>
+          <t>8586</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,98%</t>
         </is>
       </c>
     </row>
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>467310</t>
+          <t>467375</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>475129</t>
+          <t>475132</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>870747</t>
+          <t>870900</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>878508</t>
+          <t>878511</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1696</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9545</t>
+          <t>9312</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1229</t>
+          <t>1034</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12125</t>
+          <t>12351</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4216</t>
+          <t>5026</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17337</t>
+          <t>18832</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,6%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>487687</t>
+          <t>487920</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>495536</t>
+          <t>495532</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>670937</t>
+          <t>670711</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>681833</t>
+          <t>682028</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>99,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1162957</t>
+          <t>1161462</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1176078</t>
+          <t>1175268</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,57%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5479</t>
+          <t>6058</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20075</t>
+          <t>20774</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10194</t>
+          <t>10648</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>28173</t>
+          <t>29809</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,47 +2155,47 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>28781</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>18714</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>41885</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,68%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
           <t>0,44%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>1,22%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>28781</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>18664</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>41428</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1890151</t>
+          <t>1889452</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1904747</t>
+          <t>1904168</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2273189</t>
+          <t>2271553</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2291168</t>
+          <t>2290714</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4170160</t>
+          <t>4169703</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4192924</t>
+          <t>4192874</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7994</t>
+          <t>7383</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2051</t>
+          <t>1935</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12271</t>
+          <t>12057</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>3710</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16771</t>
+          <t>16321</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>464518</t>
+          <t>465129</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>502336</t>
+          <t>502550</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>512556</t>
+          <t>512672</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>970348</t>
+          <t>970798</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>983590</t>
+          <t>983409</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,62%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>962</t>
+          <t>957</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8670</t>
+          <t>9441</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,47 +3038,47 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
+          <t>0,14%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>4191</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1111</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>12396</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,56%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
           <t>0,15%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1,31%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>4191</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>1102</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>13402</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,56%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3397</t>
+          <t>3086</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17443</t>
+          <t>16769</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>652869</t>
+          <t>652098</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>660577</t>
+          <t>660582</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,49 +3151,49 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
+          <t>99,86%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>678</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>742659</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>734454</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>745739</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>99,44%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>98,34%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
           <t>99,85%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>678</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>742659</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>733448</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>745748</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,44%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>98,21%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>99,85%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>1279</t>
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1390946</t>
+          <t>1391620</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1404992</t>
+          <t>1405303</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,78%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>988</t>
+          <t>1824</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12748</t>
+          <t>12066</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2120</t>
+          <t>2111</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14214</t>
+          <t>13993</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4948</t>
+          <t>4962</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19981</t>
+          <t>20309</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>444481</t>
+          <t>445163</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>456241</t>
+          <t>455405</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>517507</t>
+          <t>517728</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>529601</t>
+          <t>529610</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>968969</t>
+          <t>968641</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>984002</t>
+          <t>983988</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>1932</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13697</t>
+          <t>14118</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6855</t>
+          <t>6870</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22420</t>
+          <t>22539</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3764,7 +3764,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10739</t>
+          <t>10724</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>29038</t>
+          <t>29452</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>532349</t>
+          <t>531928</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>544131</t>
+          <t>544114</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>701232</t>
+          <t>701113</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>716797</t>
+          <t>716782</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1240660</t>
+          <t>1240246</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1258959</t>
+          <t>1258974</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,16%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9727</t>
+          <t>9478</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28419</t>
+          <t>27855</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18056</t>
+          <t>19644</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>41584</t>
+          <t>43059</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>31692</t>
+          <t>32674</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>61375</t>
+          <t>62658</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,35%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2108907</t>
+          <t>2109471</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2127599</t>
+          <t>2127848</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2475246</t>
+          <t>2473771</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2498774</t>
+          <t>2497186</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4592781</t>
+          <t>4591498</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4622464</t>
+          <t>4621482</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,3%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3014</t>
+          <t>2873</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13949</t>
+          <t>14126</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4667,7 +4667,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6588</t>
+          <t>6143</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4212</t>
+          <t>4392</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16416</t>
+          <t>16853</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>384012</t>
+          <t>383835</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>394947</t>
+          <t>395088</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,7 +4775,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>439880</t>
+          <t>440325</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>828013</t>
+          <t>827576</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>840217</t>
+          <t>840037</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,48%</t>
         </is>
       </c>
     </row>
@@ -4975,7 +4975,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8514</t>
+          <t>8941</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2065</t>
+          <t>2114</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11756</t>
+          <t>12417</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5025,7 +5025,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16027</t>
+          <t>15973</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,7 +5055,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -5083,7 +5083,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>573819</t>
+          <t>573392</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>705258</t>
+          <t>704597</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>714949</t>
+          <t>714900</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1283320</t>
+          <t>1283374</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1296120</t>
+          <t>1296011</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,74%</t>
         </is>
       </c>
     </row>
@@ -5318,7 +5318,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7853</t>
+          <t>7230</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5333,7 +5333,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2312</t>
+          <t>2304</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13882</t>
+          <t>14159</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4240</t>
+          <t>4033</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16140</t>
+          <t>16966</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>408304</t>
+          <t>408927</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>499432</t>
+          <t>499155</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>511002</t>
+          <t>511010</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>913331</t>
+          <t>912505</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>925231</t>
+          <t>925438</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,57%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2604</t>
+          <t>2343</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12455</t>
+          <t>12368</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4009</t>
+          <t>3914</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17422</t>
+          <t>16712</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>8302</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25271</t>
+          <t>23264</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>488022</t>
+          <t>488109</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>497873</t>
+          <t>498134</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>640802</t>
+          <t>641512</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>654215</t>
+          <t>654310</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1133430</t>
+          <t>1135437</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1150649</t>
+          <t>1150399</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,28%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10835</t>
+          <t>10481</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27175</t>
+          <t>28089</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14921</t>
+          <t>14748</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>33490</t>
+          <t>33957</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>28035</t>
+          <t>29164</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>54523</t>
+          <t>56166</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,33%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1869753</t>
+          <t>1868839</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1886093</t>
+          <t>1886447</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2301530</t>
+          <t>2301063</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2320099</t>
+          <t>2320272</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4177425</t>
+          <t>4175782</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4203913</t>
+          <t>4202784</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,31%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>26188</t>
+          <t>27196</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19160</t>
+          <t>19702</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33825</t>
+          <t>37110</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,75%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>36452</t>
+          <t>39132</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>30162</t>
+          <t>31661</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>43738</t>
+          <t>47284</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>62640</t>
+          <t>66328</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>52038</t>
+          <t>53841</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>74228</t>
+          <t>77652</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>30,29%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>74041</t>
+          <t>81385</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>66404</t>
+          <t>71471</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>81069</t>
+          <t>88879</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>73,87%</t>
+          <t>74,95%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,25%</t>
+          <t>65,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,88%</t>
+          <t>81,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>99503</t>
+          <t>108610</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>92217</t>
+          <t>100458</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>105793</t>
+          <t>116081</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>73,19%</t>
+          <t>73,51%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>67,83%</t>
+          <t>68,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,81%</t>
+          <t>78,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>173544</t>
+          <t>189995</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>161956</t>
+          <t>178671</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>184146</t>
+          <t>202482</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>73,48%</t>
+          <t>74,12%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>68,57%</t>
+          <t>69,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>77,97%</t>
+          <t>78,99%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>100229</t>
+          <t>108581</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>100229</t>
+          <t>108581</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>100229</t>
+          <t>108581</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>135955</t>
+          <t>147742</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>135955</t>
+          <t>147742</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>135955</t>
+          <t>147742</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>236184</t>
+          <t>256323</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>236184</t>
+          <t>256323</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>236184</t>
+          <t>256323</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>23271</t>
+          <t>24923</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15490</t>
+          <t>16644</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33945</t>
+          <t>37563</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>37569</t>
+          <t>40114</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29900</t>
+          <t>31923</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>46988</t>
+          <t>50819</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>60840</t>
+          <t>65037</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>48651</t>
+          <t>53530</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>73907</t>
+          <t>80911</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>17,29%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>138315</t>
+          <t>168638</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>127641</t>
+          <t>155998</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>146096</t>
+          <t>176917</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>87,12%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,99%</t>
+          <t>80,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>91,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>207590</t>
+          <t>234282</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>198171</t>
+          <t>223577</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>215259</t>
+          <t>242473</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>84,68%</t>
+          <t>85,38%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>81,48%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>88,37%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>345905</t>
+          <t>402921</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>332838</t>
+          <t>387047</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>358094</t>
+          <t>414428</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>85,04%</t>
+          <t>86,1%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,83%</t>
+          <t>82,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>88,56%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>161586</t>
+          <t>193561</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>161586</t>
+          <t>193561</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>161586</t>
+          <t>193561</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>245159</t>
+          <t>274396</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>245159</t>
+          <t>274396</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>245159</t>
+          <t>274396</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>406745</t>
+          <t>467958</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>406745</t>
+          <t>467958</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>406745</t>
+          <t>467958</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>15502</t>
+          <t>16266</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9172</t>
+          <t>9515</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24478</t>
+          <t>25987</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>14325</t>
+          <t>17697</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3960</t>
+          <t>11955</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>43165</t>
+          <t>24716</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>29827</t>
+          <t>33963</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9461</t>
+          <t>24473</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>63213</t>
+          <t>45319</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>16,63%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>85806</t>
+          <t>100451</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>76830</t>
+          <t>90730</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>92136</t>
+          <t>107202</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>84,7%</t>
+          <t>86,06%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,84%</t>
+          <t>77,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>318805</t>
+          <t>138178</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>289965</t>
+          <t>131159</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>329170</t>
+          <t>143920</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>84,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>404611</t>
+          <t>238629</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>371225</t>
+          <t>227273</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>424977</t>
+          <t>248119</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>87,54%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>83,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>91,02%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>101308</t>
+          <t>116717</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>101308</t>
+          <t>116717</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>101308</t>
+          <t>116717</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>333130</t>
+          <t>155875</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>333130</t>
+          <t>155875</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>333130</t>
+          <t>155875</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>434438</t>
+          <t>272592</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>434438</t>
+          <t>272592</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>434438</t>
+          <t>272592</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16373</t>
+          <t>16443</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10563</t>
+          <t>9970</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24979</t>
+          <t>24245</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>31937</t>
+          <t>34624</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24682</t>
+          <t>26603</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>40871</t>
+          <t>45721</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>48310</t>
+          <t>51067</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>38359</t>
+          <t>40219</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>60599</t>
+          <t>63514</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>17,96%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>109756</t>
+          <t>125521</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>101150</t>
+          <t>117719</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>115566</t>
+          <t>131994</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>87,02%</t>
+          <t>88,42%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,2%</t>
+          <t>82,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>150653</t>
+          <t>177049</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>141719</t>
+          <t>165952</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>157908</t>
+          <t>185070</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>82,51%</t>
+          <t>83,64%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,62%</t>
+          <t>78,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>87,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>260410</t>
+          <t>302571</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>248121</t>
+          <t>290124</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>270361</t>
+          <t>313419</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>85,56%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,37%</t>
+          <t>82,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>88,63%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>126129</t>
+          <t>141964</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>126129</t>
+          <t>141964</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>126129</t>
+          <t>141964</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>182590</t>
+          <t>211673</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>182590</t>
+          <t>211673</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>182590</t>
+          <t>211673</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>308720</t>
+          <t>353638</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>308720</t>
+          <t>353638</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>308720</t>
+          <t>353638</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>81334</t>
+          <t>84828</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>66767</t>
+          <t>70340</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>99445</t>
+          <t>105299</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>120283</t>
+          <t>131567</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>64709</t>
+          <t>115664</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>162854</t>
+          <t>147593</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>201617</t>
+          <t>216395</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>118878</t>
+          <t>194694</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>245815</t>
+          <t>241368</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,87%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>407919</t>
+          <t>475996</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>389808</t>
+          <t>455525</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>422486</t>
+          <t>490484</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>83,38%</t>
+          <t>84,87%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,67%</t>
+          <t>81,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>776551</t>
+          <t>658120</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>733980</t>
+          <t>642094</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>832125</t>
+          <t>674023</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>86,59%</t>
+          <t>83,34%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,84%</t>
+          <t>81,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>85,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1184470</t>
+          <t>1134116</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1140272</t>
+          <t>1109143</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1267209</t>
+          <t>1155817</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>83,98%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,27%</t>
+          <t>82,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>85,58%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>489253</t>
+          <t>560824</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>489253</t>
+          <t>560824</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>489253</t>
+          <t>560824</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>896834</t>
+          <t>789687</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>896834</t>
+          <t>789687</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>896834</t>
+          <t>789687</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1386087</t>
+          <t>1350511</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1386087</t>
+          <t>1350511</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1386087</t>
+          <t>1350511</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">

--- a/data/trans_orig/P2C_R1-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P2C_R1-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son remunerados en 2007 (tasa de respuesta: 99,95%)</t>
+          <t>Población según si convive con al menos un miembro que requiere cuidados y estos son remunerados en 2007 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son remunerados en 2012 (tasa de respuesta: 99,27%)</t>
+          <t>Población según si convive con al menos un miembro que requiere cuidados y estos son remunerados en 2012 (tasa de respuesta: 99,27%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son remunerados en 2016 (tasa de respuesta: 94,57%)</t>
+          <t>Población según si convive con al menos un miembro que requiere cuidados y estos son remunerados en 2016 (tasa de respuesta: 94,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen al menos un miembro que requiere cuidados y estos son remunerados en 2023 (tasa de respuesta: 99,88%)</t>
+          <t>Población según si convive con al menos un miembro que requiere cuidados y estos son remunerados en 2023 (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
